--- a/Base de dados/GGR Bets Brasil.xlsx
+++ b/Base de dados/GGR Bets Brasil.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Downloads\Inadimplência\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Downloads\Projetos V - Macro\Base de dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B79ADB6-A364-4395-A6D9-2E0EBC4A6EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA5E954-D58A-46C8-94B4-EB9842AB1133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5C2206B1-3AB1-4097-8C6D-27C4014EC308}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Casas de apostas têm projeções de crescimento constante nos próximos anos</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -143,6 +146,1140 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GGR Operações Offshore</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="002060"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Planilha1!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2030</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$B$2:$K$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2975-4C38-B905-149B003D13B8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GGR Operações Nacionais</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-2975-4C38-B905-149B003D13B8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-2975-4C38-B905-149B003D13B8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-2975-4C38-B905-149B003D13B8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-2975-4C38-B905-149B003D13B8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Planilha1!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2030</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2975-4C38-B905-149B003D13B8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="133031487"/>
+        <c:axId val="113595727"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="133031487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="113595727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="113595727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="133031487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F20230E-7C89-86D6-477C-18E0A47D8438}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -630,6 +1767,11 @@
         <v>2</v>
       </c>
     </row>
+    <row r="10" spans="1:11">
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="11" spans="1:11">
       <c r="A11" s="3" t="s">
         <v>3</v>
@@ -637,5 +1779,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>